--- a/BVSimulationFiles/56.xlsx
+++ b/BVSimulationFiles/56.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="O2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="U2" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="O3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007288801571709235</v>
+        <v>0.01457760314341847</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/56.xlsx
+++ b/BVSimulationFiles/56.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01457760314341847</v>
+        <v>0.1457760314341847</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/56.xlsx
+++ b/BVSimulationFiles/56.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1457760314341847</v>
+        <v>0.455814852398232</v>
       </c>
     </row>
   </sheetData>
